--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2020_atacama.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2020_atacama.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:42</t>
+    <t xml:space="preserve">2026-10-05 02:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>352568.72</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>351872.91</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -855,7 +855,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>364702.12</v>
+        <v>364702.13</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>334453.53</v>
@@ -913,7 +913,7 @@
         <v>356660.5</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -932,7 +932,7 @@
         <v>24</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>366025.12</v>
+        <v>366025.13</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>332082.44</v>
@@ -987,7 +987,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>374326.12</v>
+        <v>374326.13</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>338426.22</v>
@@ -1287,7 +1287,7 @@
         <v>441726.59</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1416,7 +1416,7 @@
         <v>68</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>496332.62</v>
+        <v>496332.63</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>432824.94</v>
@@ -1529,7 +1529,7 @@
         <v>514005.09</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>529298.19</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
@@ -1603,7 +1603,7 @@
         <v>85</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>544222.12</v>
+        <v>544222.13</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>461908.94</v>
